--- a/books.xlsx
+++ b/books.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Book club\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Book club\Book_club -for git\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="1050" yWindow="0" windowWidth="27750" windowHeight="13020"/>
+    <workbookView xWindow="2100" yWindow="0" windowWidth="27750" windowHeight="13020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -434,7 +434,7 @@
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" style="1"/>

--- a/books.xlsx
+++ b/books.xlsx
@@ -32,9 +32,6 @@
     <t>Author</t>
   </si>
   <si>
-    <t xml:space="preserve">Status </t>
-  </si>
-  <si>
     <t>Contact</t>
   </si>
   <si>
@@ -99,6 +96,9 @@
   </si>
   <si>
     <t>Joe</t>
+  </si>
+  <si>
+    <t>Status</t>
   </si>
 </sst>
 </file>
@@ -448,122 +448,122 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="C4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="C5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="C7" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="C8" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="C9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
